--- a/paper_tables/Table_4_Graphene_TPMS_Topologies.xlsx
+++ b/paper_tables/Table_4_Graphene_TPMS_Topologies.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TPMS_Topologies" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TPMS Leaderboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -89,16 +89,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,262 +465,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Topology</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cif_file</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Num_Atoms</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Density_g_cm3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Band_Gap_eV</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Formation_Energy_eV_atom</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Bulk_Modulus_GPa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Shear_Modulus_GPa</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Young_Modulus_GPa</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>E_ads_DFT_eV</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TPMS_Composite_Score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Rank</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Topology</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atoms</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Density</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Eg (eV)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Ef (eV/at)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>K (GPa)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>G (GPa)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E (GPa)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Eads (eV)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>SHEET_DIAMOND</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Diamond (D)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>graphene_sheet_diamond.cif</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>332</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>2.397</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>185.4</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>236.8</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="K2" s="2" t="n">
+      <c r="F2" s="3" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.9393783695822653</v>
+      </c>
+      <c r="L2" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Gyroid (G)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>graphene_sheet_gyroid.cif</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>244</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.8256527030526872</v>
+      </c>
+      <c r="L3" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>SHEET_GYROID</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>244</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>1.925</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>219</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>-2.48</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0.857</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>IWP (I-WP)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>graphene_sheet_iwp.cif</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.8072377411534717</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>SHEET_NEOVIUS</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>134.2</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.465</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Neovius (N)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>graphene_sheet_neovius.cif</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.7086941624430343</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>SHEET_IWP</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>228</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>2.259</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>178.4</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0.449</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Primitive (P)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>graphene_sheet_primitive.cif</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.3398151492458626</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SHEET_PRIMITIVE</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.251</v>
       </c>
     </row>
   </sheetData>
